--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260713.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.97%</t>
+          <t>10.80%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>10.08%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>8.83%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.48%</t>
+          <t>7.35%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,221</t>
+          <t>61,521</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>61,521</t>
+          <t>20,221</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1144,156 +1144,156 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,135</t>
+          <t>49,071</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>49,071</t>
+          <t>28,767</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>28,767</t>
+          <t>21,609</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>21,609</t>
+          <t>99,194</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>99,194</t>
+          <t>5,135</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,396</t>
+          <t>78,337</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,828</t>
+          <t>9,396</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>78,337</t>
+          <t>13,828</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1342,51 +1342,51 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>11,109</t>
+          <t>152,287</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>152,287</t>
+          <t>11,109</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>14,007</t>
+          <t>45,373</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>45,373</t>
+          <t>14,007</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1540,51 +1540,51 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,133</t>
+          <t>3,810</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,810</t>
+          <t>6,133</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>117,734,603</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
